--- a/tests/testdata/excel/シート表示状態.xlsx
+++ b/tests/testdata/excel/シート表示状態.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C91ADCA-E0AB-415B-9EEC-81E0D9C28B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DD05DD8-4788-4BE1-9315-2BFCDEF15270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{201D234C-3741-4C93-8A06-30923216CF3E}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{E0ED29A2-C0F3-44EC-87F4-9775C6D55154}"/>
   </bookViews>
   <sheets>
     <sheet name="表示" sheetId="1" r:id="rId1"/>
@@ -214,7 +214,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7DB4-4A17-8AE3-EFFE35701693}"/>
+              <c16:uniqueId val="{00000000-6143-4C09-9FD6-3FD3B9448E35}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -227,11 +227,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="1553097215"/>
-        <c:axId val="1553096255"/>
+        <c:axId val="994367695"/>
+        <c:axId val="994368175"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1553097215"/>
+        <c:axId val="994367695"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -241,7 +241,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1553096255"/>
+        <c:crossAx val="994368175"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -249,7 +249,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1553096255"/>
+        <c:axId val="994368175"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -260,7 +260,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1553097215"/>
+        <c:crossAx val="994367695"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -284,7 +284,7 @@
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{1DCAC0FB-C964-45E1-9DE6-629F917F4075}">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{40680CB8-CA10-42DE-9623-DD9177638DF5}">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -301,7 +301,7 @@
         <xdr:cNvPr id="2" name="グラフ 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBE69C20-2BD4-9A30-A256-0944AD0FF923}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA05D84D-D9DC-940C-182E-AB140E60614D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B368AB44-C245-492F-A128-BAB64112A95A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0374418D-D93A-416C-ACF2-D49EE6583582}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -683,7 +683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBB58D7-1E77-4160-AC4A-E9E015DB9E38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BFC700-229C-4F3A-91C0-3BF33AFFD99F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -699,7 +699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6336C6EE-FA44-4B34-9C45-5CD1820BB54D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A03C57-BC74-4F73-B0B9-616DFD68A3A0}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -715,7 +715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAA6C44-10C8-48FC-B5A5-A87B4C811AAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{645F601B-330E-4D24-808B-2DB36BFC6340}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>

--- a/tests/testdata/excel/シート表示状態.xlsx
+++ b/tests/testdata/excel/シート表示状態.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DD05DD8-4788-4BE1-9315-2BFCDEF15270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8685D1AA-92F0-4E91-BDE5-2CF7D07A60B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{E0ED29A2-C0F3-44EC-87F4-9775C6D55154}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{3DD6E605-F1C0-4C92-906E-1E37718358A1}"/>
   </bookViews>
   <sheets>
     <sheet name="表示" sheetId="1" r:id="rId1"/>
@@ -214,7 +214,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6143-4C09-9FD6-3FD3B9448E35}"/>
+              <c16:uniqueId val="{00000000-910C-47A8-82B1-C2C83B6E8498}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -227,11 +227,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="994367695"/>
-        <c:axId val="994368175"/>
+        <c:axId val="1759552352"/>
+        <c:axId val="1759552832"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="994367695"/>
+        <c:axId val="1759552352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -241,7 +241,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="994368175"/>
+        <c:crossAx val="1759552832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -249,7 +249,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="994368175"/>
+        <c:axId val="1759552832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -260,7 +260,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="994367695"/>
+        <c:crossAx val="1759552352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -284,7 +284,7 @@
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{40680CB8-CA10-42DE-9623-DD9177638DF5}">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{0CCFBD91-8C03-4DEE-B667-AF7938098FCB}">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -301,7 +301,7 @@
         <xdr:cNvPr id="2" name="グラフ 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA05D84D-D9DC-940C-182E-AB140E60614D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48E338B7-1DDD-A817-FA66-E5124A8651CB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0374418D-D93A-416C-ACF2-D49EE6583582}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A3BC32-CAC2-4292-8670-6A4FDE189EE2}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -683,7 +683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BFC700-229C-4F3A-91C0-3BF33AFFD99F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8E18E7A-F55E-45D9-AEB5-2FFB4AE2050A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -699,7 +699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A03C57-BC74-4F73-B0B9-616DFD68A3A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E363E766-6301-491A-8AD8-DAF5BEEFD4CB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -715,7 +715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{645F601B-330E-4D24-808B-2DB36BFC6340}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C81680-0278-4DA9-B480-9B31E35B9060}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
